--- a/data/trans_dic/P39A2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,86; 74,94</t>
+          <t>66,66; 75,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,53; 70,08</t>
+          <t>62,79; 70,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,91; 71,57</t>
+          <t>65,87; 71,59</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,97; 77,57</t>
+          <t>68,5; 77,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,96; 66,75</t>
+          <t>57,35; 66,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,91; 70,97</t>
+          <t>65,03; 71,17</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,45; 92,83</t>
+          <t>66,48; 92,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55,22; 68,12</t>
+          <t>54,57; 67,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,13; 89,88</t>
+          <t>64,86; 89,29</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,53; 75,09</t>
+          <t>68,32; 75,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,3; 86,7</t>
+          <t>64,2; 85,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,31; 80,6</t>
+          <t>68,37; 82,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,41; 76,98</t>
+          <t>67,92; 77,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,97; 70,04</t>
+          <t>45,55; 70,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,11; 71,37</t>
+          <t>52,1; 70,97</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,99; 84,05</t>
+          <t>62,35; 83,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72,13; 78,4</t>
+          <t>71,95; 78,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,26; 78,52</t>
+          <t>70,97; 78,01</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,01; 81,62</t>
+          <t>70,88; 80,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,37; 74,51</t>
+          <t>64,37; 74,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,24; 75,16</t>
+          <t>68,13; 74,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>322718; 361718</t>
+          <t>321724; 363375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>264124; 296014</t>
+          <t>265216; 297123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>596543; 647740</t>
+          <t>596140; 647877</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>299453; 336778</t>
+          <t>297389; 335597</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206811; 238143</t>
+          <t>204631; 237315</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513446; 561349</t>
+          <t>514353; 562905</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>425117; 593860</t>
+          <t>425273; 589435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83330; 102801</t>
+          <t>82348; 102438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>514938; 710657</t>
+          <t>512815; 705938</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>649659; 711848</t>
+          <t>647635; 711604</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>595014; 802318</t>
+          <t>594071; 793381</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1279696; 1510022</t>
+          <t>1280852; 1547837</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>273492; 312314</t>
+          <t>275577; 313321</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>304769; 496790</t>
+          <t>323089; 497240</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>569887; 795717</t>
+          <t>580934; 791327</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>125674; 167686</t>
+          <t>124382; 166242</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>468537; 509263</t>
+          <t>467318; 509005</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>605033; 666693</t>
+          <t>602571; 662356</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2208178; 2538241</t>
+          <t>2204272; 2497915</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2068951; 2395099</t>
+          <t>2069123; 2379410</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4315525; 4752951</t>
+          <t>4308847; 4736427</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A2_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,66; 75,29</t>
+          <t>67,26; 75,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,79; 70,35</t>
+          <t>61,65; 69,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,87; 71,59</t>
+          <t>65,69; 71,46</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,5; 77,3</t>
+          <t>69,68; 77,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,35; 66,51</t>
+          <t>57,61; 66,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,03; 71,17</t>
+          <t>65,42; 71,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,48; 92,14</t>
+          <t>62,09; 71,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,57; 67,88</t>
+          <t>55,7; 67,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,86; 89,29</t>
+          <t>60,9; 68,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68,32; 75,06</t>
+          <t>68,05; 74,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,2; 85,74</t>
+          <t>62,18; 67,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,37; 82,62</t>
+          <t>66,17; 70,43</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,92; 77,22</t>
+          <t>67,28; 76,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,55; 70,11</t>
+          <t>65,55; 71,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,1; 70,97</t>
+          <t>67,31; 72,22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,35; 83,33</t>
+          <t>65,76; 84,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,95; 78,36</t>
+          <t>72,02; 78,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,97; 78,01</t>
+          <t>72,24; 78,53</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,88; 80,32</t>
+          <t>69,47; 72,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,37; 74,03</t>
+          <t>66,13; 69,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,13; 74,9</t>
+          <t>68,3; 70,54</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>342855</t>
+          <t>374539</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280513</t>
+          <t>302316</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623368</t>
+          <t>676855</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>321724; 363375</t>
+          <t>353424; 394236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>265216; 297123</t>
+          <t>283893; 318809</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>596140; 647877</t>
+          <t>647682; 704504</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>317858</t>
+          <t>341843</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>221932</t>
+          <t>244972</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>539790</t>
+          <t>586815</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>297389; 335597</t>
+          <t>322491; 359031</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204631; 237315</t>
+          <t>226450; 260826</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514353; 562905</t>
+          <t>559945; 608943</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>512485</t>
+          <t>290193</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92770</t>
+          <t>104276</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605255</t>
+          <t>394469</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>425273; 589435</t>
+          <t>270641; 312746</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82348; 102438</t>
+          <t>94398; 114655</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>512815; 705938</t>
+          <t>368664; 413423</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>681351</t>
+          <t>734273</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>674949</t>
+          <t>521059</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1356299</t>
+          <t>1255332</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>647635; 711604</t>
+          <t>703132; 766415</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>594071; 793381</t>
+          <t>498507; 544859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1280852; 1547837</t>
+          <t>1214192; 1292331</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>294371</t>
+          <t>337612</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>441654</t>
+          <t>488883</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>736025</t>
+          <t>826496</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>275577; 313321</t>
+          <t>314666; 358237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>323089; 497240</t>
+          <t>467944; 508154</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>580934; 791327</t>
+          <t>795390; 853397</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>147541</t>
+          <t>148353</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>489410</t>
+          <t>543182</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>636951</t>
+          <t>691535</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>124382; 166242</t>
+          <t>127607; 164021</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>467318; 509005</t>
+          <t>520764; 565328</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>602571; 662356</t>
+          <t>662477; 720201</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2296461</t>
+          <t>2226812</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2201227</t>
+          <t>2204689</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4497689</t>
+          <t>4431501</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2204272; 2497915</t>
+          <t>2166767; 2275642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2069123; 2379410</t>
+          <t>2157085; 2252632</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4308847; 4736427</t>
+          <t>4358221; 4500831</t>
         </is>
       </c>
     </row>
